--- a/business_forms/019_global_market_strategy_program_application--business_forms.xlsx
+++ b/business_forms/019_global_market_strategy_program_application--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'strategy'}</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Strategy'}</t>
+          <t>Strategy</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'market_research'}</t>
+          <t>market_research</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Market Research'}</t>
+          <t>Market Research</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'business_development'}</t>
+          <t>business_development</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Business Development'}</t>
+          <t>Business Development</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'in-house'}</t>
+          <t>in-house</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'In-House'}</t>
+          <t>In-House</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'partnered'}</t>
+          <t>partnered</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Partnered'}</t>
+          <t>Partnered</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'1-10'}</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': '1-10'}</t>
+          <t>1-10</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'11-50'}</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': '11-50'}</t>
+          <t>11-50</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'51-200'}</t>
+          <t>51-200</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': '51-200'}</t>
+          <t>51-200</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'201-500'}</t>
+          <t>201-500</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': '201-500'}</t>
+          <t>201-500</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'501-1000'}</t>
+          <t>501-1000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': '501-1000'}</t>
+          <t>501-1000</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'1001'}</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '1001'}</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'healthcare'}</t>
+          <t>healthcare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Healthcare'}</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'retail'}</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Retail'}</t>
+          <t>Retail</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Full Time'}</t>
+          <t>Full Time</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Part Time'}</t>
+          <t>Part Time</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Freelance'}</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
